--- a/assets.xlsx
+++ b/assets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sgvggroup-my.sharepoint.com/personal/neeraj_balodi_sgvgroup_in/Documents/Documents/GitHub/Ops Desk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Neeraj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_F25DC773A252ABDACC10483B599B48745ADE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E83249A-56E9-491A-A59A-0AB7BB33825D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E781B9B-C829-497A-A036-68FB5B9A3543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="525" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site List" sheetId="2" r:id="rId1"/>
@@ -30,15 +30,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="293">
   <si>
     <t>Name</t>
   </si>
@@ -794,13 +791,136 @@
   </si>
   <si>
     <t>Head Office</t>
+  </si>
+  <si>
+    <t>Signature Global CITY Sec-63</t>
+  </si>
+  <si>
+    <t>Signature Global Prime Sec-63</t>
+  </si>
+  <si>
+    <t>Signature dakshin</t>
+  </si>
+  <si>
+    <t>park 4,5 Facility</t>
+  </si>
+  <si>
+    <t>165 A</t>
+  </si>
+  <si>
+    <t>Gym golf summit plaza</t>
+  </si>
+  <si>
+    <t>Millennia 1 at Sec-37D</t>
+  </si>
+  <si>
+    <t>ASHIYANA HOME</t>
+  </si>
+  <si>
+    <t>Urban Quebe</t>
+  </si>
+  <si>
+    <t>Good earth</t>
+  </si>
+  <si>
+    <t>Whiteland Project-103</t>
+  </si>
+  <si>
+    <t>Whiteland Sales Gallery-103</t>
+  </si>
+  <si>
+    <t>MVN Mall</t>
+  </si>
+  <si>
+    <t>Infra 93 Project Revenue Road</t>
+  </si>
+  <si>
+    <t>Infra 92 Project</t>
+  </si>
+  <si>
+    <t>Whiteland Sector-76</t>
+  </si>
+  <si>
+    <t>397-398</t>
+  </si>
+  <si>
+    <t>Signature Global 25 Acre</t>
+  </si>
+  <si>
+    <t>SGV HO</t>
+  </si>
+  <si>
+    <t>SCO 83 DLF</t>
+  </si>
+  <si>
+    <t>N10</t>
+  </si>
+  <si>
+    <t>N11</t>
+  </si>
+  <si>
+    <t>N12</t>
+  </si>
+  <si>
+    <t>N13</t>
+  </si>
+  <si>
+    <t>N14</t>
+  </si>
+  <si>
+    <t>N15</t>
+  </si>
+  <si>
+    <t>N16</t>
+  </si>
+  <si>
+    <t>N17</t>
+  </si>
+  <si>
+    <t>N18</t>
+  </si>
+  <si>
+    <t>N19</t>
+  </si>
+  <si>
+    <t>Deepak Sahu</t>
+  </si>
+  <si>
+    <t>Shiv Shakti</t>
+  </si>
+  <si>
+    <t>Prashant bidhuri</t>
+  </si>
+  <si>
+    <t>Anand kumar</t>
+  </si>
+  <si>
+    <t>Jagat</t>
+  </si>
+  <si>
+    <t>Dipendra</t>
+  </si>
+  <si>
+    <t>Ravi Shankar</t>
+  </si>
+  <si>
+    <t>Dhiraj Kumar</t>
+  </si>
+  <si>
+    <t>Subodh Singh</t>
+  </si>
+  <si>
+    <t>Mausam Kumar</t>
+  </si>
+  <si>
+    <t>DGM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -918,7 +1038,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1061,6 +1181,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1078,7 +1209,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1254,6 +1385,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1540,15 +1675,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D9BF060-BE15-409D-9B19-04A42B13D1BE}">
-  <dimension ref="A1:C209"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:C231"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.453125" customWidth="1"/>
     <col min="2" max="2" width="12.26953125" customWidth="1"/>
     <col min="3" max="3" width="37.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="33" t="s">
         <v>3</v>
       </c>
@@ -1559,7 +1694,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="36">
         <v>0</v>
       </c>
@@ -1570,7 +1705,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="36">
         <v>1</v>
       </c>
@@ -1581,7 +1716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="36">
         <v>1</v>
       </c>
@@ -1592,7 +1727,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="36">
         <v>1</v>
       </c>
@@ -1603,7 +1738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="36">
         <v>1</v>
       </c>
@@ -1614,7 +1749,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="36">
         <v>1</v>
       </c>
@@ -1625,7 +1760,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="36">
         <v>1</v>
       </c>
@@ -1636,7 +1771,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="36">
         <v>1</v>
       </c>
@@ -1647,7 +1782,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="36">
         <v>1</v>
       </c>
@@ -1658,7 +1793,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="36">
         <v>1</v>
       </c>
@@ -1669,7 +1804,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="36">
         <v>1</v>
       </c>
@@ -1680,7 +1815,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="36">
         <v>1</v>
       </c>
@@ -1691,7 +1826,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="36">
         <v>1</v>
       </c>
@@ -1702,7 +1837,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="36">
         <v>1</v>
       </c>
@@ -1713,7 +1848,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="36">
         <v>1</v>
       </c>
@@ -1724,7 +1859,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="36">
         <v>1</v>
       </c>
@@ -1735,7 +1870,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="36">
         <v>1</v>
       </c>
@@ -1746,7 +1881,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="36">
         <v>1</v>
       </c>
@@ -1757,7 +1892,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="36">
         <v>1</v>
       </c>
@@ -1768,7 +1903,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="36">
         <v>1</v>
       </c>
@@ -1779,7 +1914,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="36">
         <v>1</v>
       </c>
@@ -1790,7 +1925,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="36">
         <v>1</v>
       </c>
@@ -1801,7 +1936,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="36">
         <v>1</v>
       </c>
@@ -1812,7 +1947,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="36">
         <v>1</v>
       </c>
@@ -1823,7 +1958,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="36">
         <v>1</v>
       </c>
@@ -1834,7 +1969,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="36">
         <v>1</v>
       </c>
@@ -1845,7 +1980,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="36">
         <v>1</v>
       </c>
@@ -1856,7 +1991,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="36">
         <v>1</v>
       </c>
@@ -1867,7 +2002,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="36">
         <v>1</v>
       </c>
@@ -1878,7 +2013,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="36">
         <v>1</v>
       </c>
@@ -1889,7 +2024,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="36">
         <v>1</v>
       </c>
@@ -1900,7 +2035,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="36">
         <v>1</v>
       </c>
@@ -1911,7 +2046,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="36">
         <v>1</v>
       </c>
@@ -1922,7 +2057,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="36">
         <v>1</v>
       </c>
@@ -1933,7 +2068,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="36">
         <v>1</v>
       </c>
@@ -1944,7 +2079,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="36">
         <v>1</v>
       </c>
@@ -1955,7 +2090,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="36">
         <v>1</v>
       </c>
@@ -1966,7 +2101,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="36">
         <v>1</v>
       </c>
@@ -1977,7 +2112,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="36">
         <v>1</v>
       </c>
@@ -1988,7 +2123,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="36">
         <v>1</v>
       </c>
@@ -1999,7 +2134,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="36">
         <v>1</v>
       </c>
@@ -2010,7 +2145,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="36">
         <v>1</v>
       </c>
@@ -2021,7 +2156,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="36">
         <v>1</v>
       </c>
@@ -2032,7 +2167,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="36">
         <v>2</v>
       </c>
@@ -2043,7 +2178,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="36">
         <v>2</v>
       </c>
@@ -2054,7 +2189,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="36">
         <v>2</v>
       </c>
@@ -2065,7 +2200,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="36">
         <v>2</v>
       </c>
@@ -2076,7 +2211,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="36">
         <v>2</v>
       </c>
@@ -2087,7 +2222,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="36">
         <v>2</v>
       </c>
@@ -2098,7 +2233,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="36">
         <v>2</v>
       </c>
@@ -2109,7 +2244,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="36">
         <v>2</v>
       </c>
@@ -2120,7 +2255,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="36">
         <v>2</v>
       </c>
@@ -2131,7 +2266,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="36">
         <v>2</v>
       </c>
@@ -2142,7 +2277,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="36">
         <v>2</v>
       </c>
@@ -2153,7 +2288,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="36">
         <v>2</v>
       </c>
@@ -2164,7 +2299,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="36">
         <v>2</v>
       </c>
@@ -2175,7 +2310,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="36">
         <v>2</v>
       </c>
@@ -2186,7 +2321,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="36">
         <v>2</v>
       </c>
@@ -2197,7 +2332,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="36">
         <v>2</v>
       </c>
@@ -2208,7 +2343,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" s="36">
         <v>2</v>
       </c>
@@ -2219,7 +2354,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" s="36">
         <v>2</v>
       </c>
@@ -2230,7 +2365,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" s="36">
         <v>2</v>
       </c>
@@ -2241,7 +2376,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" s="36">
         <v>2</v>
       </c>
@@ -2252,7 +2387,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" s="36">
         <v>2</v>
       </c>
@@ -2263,7 +2398,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" s="36">
         <v>2</v>
       </c>
@@ -2274,7 +2409,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" s="36">
         <v>2</v>
       </c>
@@ -2285,7 +2420,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" s="36">
         <v>2</v>
       </c>
@@ -2296,7 +2431,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" s="36">
         <v>2</v>
       </c>
@@ -2307,7 +2442,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" s="36">
         <v>2</v>
       </c>
@@ -2318,7 +2453,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" s="36">
         <v>2</v>
       </c>
@@ -2329,7 +2464,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" s="36">
         <v>2</v>
       </c>
@@ -2340,7 +2475,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" s="36">
         <v>2</v>
       </c>
@@ -2351,7 +2486,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" s="36">
         <v>2</v>
       </c>
@@ -2362,7 +2497,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" s="36">
         <v>2</v>
       </c>
@@ -2373,7 +2508,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" s="36">
         <v>2</v>
       </c>
@@ -2384,7 +2519,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" s="36">
         <v>2</v>
       </c>
@@ -2395,7 +2530,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" s="36">
         <v>2</v>
       </c>
@@ -2406,7 +2541,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" s="36">
         <v>2</v>
       </c>
@@ -2417,7 +2552,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" s="36">
         <v>2</v>
       </c>
@@ -2428,7 +2563,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" s="36">
         <v>2</v>
       </c>
@@ -2439,7 +2574,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" s="36">
         <v>2</v>
       </c>
@@ -2450,7 +2585,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" s="36">
         <v>2</v>
       </c>
@@ -2461,7 +2596,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" s="36">
         <v>2</v>
       </c>
@@ -2472,7 +2607,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" s="36">
         <v>2</v>
       </c>
@@ -2483,7 +2618,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" s="36">
         <v>2</v>
       </c>
@@ -2494,7 +2629,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" s="36">
         <v>2</v>
       </c>
@@ -2505,7 +2640,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A88" s="36">
         <v>2</v>
       </c>
@@ -2516,7 +2651,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A89" s="36">
         <v>2</v>
       </c>
@@ -2527,7 +2662,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A90" s="36">
         <v>2</v>
       </c>
@@ -2538,7 +2673,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A91" s="36">
         <v>2</v>
       </c>
@@ -2549,7 +2684,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A92" s="36">
         <v>2</v>
       </c>
@@ -2560,7 +2695,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A93" s="36">
         <v>2</v>
       </c>
@@ -2571,7 +2706,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A94" s="36">
         <v>3</v>
       </c>
@@ -2582,7 +2717,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A95" s="36">
         <v>3</v>
       </c>
@@ -2593,7 +2728,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A96" s="36">
         <v>3</v>
       </c>
@@ -2604,7 +2739,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A97" s="36">
         <v>3</v>
       </c>
@@ -2615,7 +2750,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A98" s="36">
         <v>3</v>
       </c>
@@ -2626,7 +2761,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A99" s="36">
         <v>3</v>
       </c>
@@ -2637,7 +2772,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A100" s="36">
         <v>3</v>
       </c>
@@ -2648,7 +2783,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A101" s="36">
         <v>3</v>
       </c>
@@ -2659,7 +2794,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A102" s="36">
         <v>3</v>
       </c>
@@ -2670,7 +2805,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A103" s="36">
         <v>3</v>
       </c>
@@ -2681,7 +2816,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A104" s="36">
         <v>3</v>
       </c>
@@ -2692,7 +2827,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A105" s="36">
         <v>3</v>
       </c>
@@ -2703,7 +2838,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A106" s="36">
         <v>3</v>
       </c>
@@ -2714,7 +2849,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A107" s="36">
         <v>3</v>
       </c>
@@ -2725,7 +2860,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A108" s="36">
         <v>3</v>
       </c>
@@ -2736,7 +2871,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A109" s="36">
         <v>3</v>
       </c>
@@ -2747,7 +2882,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A110" s="36">
         <v>3</v>
       </c>
@@ -2758,7 +2893,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A111" s="36">
         <v>3</v>
       </c>
@@ -2769,7 +2904,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A112" s="36">
         <v>3</v>
       </c>
@@ -2780,7 +2915,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A113" s="36">
         <v>3</v>
       </c>
@@ -2791,7 +2926,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A114" s="36">
         <v>3</v>
       </c>
@@ -2802,7 +2937,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A115" s="36">
         <v>3</v>
       </c>
@@ -2813,7 +2948,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A116" s="36">
         <v>3</v>
       </c>
@@ -2824,7 +2959,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A117" s="36">
         <v>3</v>
       </c>
@@ -2835,7 +2970,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A118" s="36">
         <v>3</v>
       </c>
@@ -2846,7 +2981,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A119" s="36">
         <v>3</v>
       </c>
@@ -2857,7 +2992,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A120" s="36">
         <v>3</v>
       </c>
@@ -2868,7 +3003,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A121" s="36">
         <v>3</v>
       </c>
@@ -2879,7 +3014,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" s="36">
         <v>3</v>
       </c>
@@ -2890,7 +3025,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" s="36">
         <v>3</v>
       </c>
@@ -2901,7 +3036,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A124" s="36">
         <v>3</v>
       </c>
@@ -2912,7 +3047,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A125" s="36">
         <v>3</v>
       </c>
@@ -2923,7 +3058,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A126" s="36">
         <v>3</v>
       </c>
@@ -2934,7 +3069,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A127" s="36">
         <v>3</v>
       </c>
@@ -2945,7 +3080,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A128" s="36">
         <v>3</v>
       </c>
@@ -2956,7 +3091,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A129" s="36">
         <v>3</v>
       </c>
@@ -2967,7 +3102,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A130" s="36">
         <v>3</v>
       </c>
@@ -2978,7 +3113,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A131" s="36">
         <v>3</v>
       </c>
@@ -2989,7 +3124,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A132" s="36">
         <v>3</v>
       </c>
@@ -3000,7 +3135,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A133" s="36">
         <v>3</v>
       </c>
@@ -3011,7 +3146,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A134" s="36">
         <v>3</v>
       </c>
@@ -3022,7 +3157,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="135" spans="1:3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A135" s="36">
         <v>4</v>
       </c>
@@ -3033,7 +3168,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="136" spans="1:3">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A136" s="36">
         <v>4</v>
       </c>
@@ -3044,7 +3179,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="137" spans="1:3">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A137" s="36">
         <v>4</v>
       </c>
@@ -3055,7 +3190,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="138" spans="1:3">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A138" s="36">
         <v>4</v>
       </c>
@@ -3066,7 +3201,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="139" spans="1:3">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" s="36">
         <v>4</v>
       </c>
@@ -3077,7 +3212,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" s="36">
         <v>4</v>
       </c>
@@ -3088,7 +3223,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="141" spans="1:3">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A141" s="36">
         <v>4</v>
       </c>
@@ -3099,7 +3234,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="142" spans="1:3">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A142" s="36">
         <v>4</v>
       </c>
@@ -3110,7 +3245,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="143" spans="1:3">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A143" s="36">
         <v>4</v>
       </c>
@@ -3121,7 +3256,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A144" s="36">
         <v>4</v>
       </c>
@@ -3132,7 +3267,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A145" s="36">
         <v>4</v>
       </c>
@@ -3143,7 +3278,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A146" s="36">
         <v>4</v>
       </c>
@@ -3154,7 +3289,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A147" s="36">
         <v>4</v>
       </c>
@@ -3165,7 +3300,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A148" s="36">
         <v>4</v>
       </c>
@@ -3176,7 +3311,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A149" s="36">
         <v>4</v>
       </c>
@@ -3187,7 +3322,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A150" s="36">
         <v>4</v>
       </c>
@@ -3198,7 +3333,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A151" s="36">
         <v>4</v>
       </c>
@@ -3209,7 +3344,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A152" s="36">
         <v>4</v>
       </c>
@@ -3220,7 +3355,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A153" s="36">
         <v>4</v>
       </c>
@@ -3231,7 +3366,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A154" s="36">
         <v>4</v>
       </c>
@@ -3242,7 +3377,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A155" s="36">
         <v>4</v>
       </c>
@@ -3253,7 +3388,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A156" s="36">
         <v>4</v>
       </c>
@@ -3264,7 +3399,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="157" spans="1:3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A157" s="36">
         <v>4</v>
       </c>
@@ -3275,7 +3410,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" s="36">
         <v>4</v>
       </c>
@@ -3286,7 +3421,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" s="36">
         <v>4</v>
       </c>
@@ -3297,7 +3432,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="160" spans="1:3">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" s="36">
         <v>4</v>
       </c>
@@ -3308,7 +3443,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="161" spans="1:3">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" s="36">
         <v>4</v>
       </c>
@@ -3319,7 +3454,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="162" spans="1:3">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" s="36">
         <v>4</v>
       </c>
@@ -3330,7 +3465,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="163" spans="1:3">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A163" s="36">
         <v>4</v>
       </c>
@@ -3341,7 +3476,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A164" s="36">
         <v>4</v>
       </c>
@@ -3352,7 +3487,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="165" spans="1:3">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A165" s="36">
         <v>4</v>
       </c>
@@ -3363,7 +3498,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="166" spans="1:3">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A166" s="36">
         <v>4</v>
       </c>
@@ -3374,7 +3509,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="167" spans="1:3">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A167" s="36">
         <v>4</v>
       </c>
@@ -3385,7 +3520,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A168" s="36">
         <v>4</v>
       </c>
@@ -3396,7 +3531,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="169" spans="1:3">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A169" s="36">
         <v>4</v>
       </c>
@@ -3407,7 +3542,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A170" s="36">
         <v>4</v>
       </c>
@@ -3418,7 +3553,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A171" s="36">
         <v>4</v>
       </c>
@@ -3429,7 +3564,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="172" spans="1:3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A172" s="36">
         <v>4</v>
       </c>
@@ -3440,7 +3575,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A173" s="36">
         <v>4</v>
       </c>
@@ -3451,7 +3586,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A174" s="36">
         <v>4</v>
       </c>
@@ -3462,7 +3597,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A175" s="36">
         <v>4</v>
       </c>
@@ -3473,7 +3608,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A176" s="36">
         <v>4</v>
       </c>
@@ -3484,7 +3619,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A177" s="36">
         <v>4</v>
       </c>
@@ -3495,7 +3630,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="178" spans="1:3">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A178" s="36">
         <v>4</v>
       </c>
@@ -3506,7 +3641,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="179" spans="1:3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A179" s="36">
         <v>4</v>
       </c>
@@ -3517,7 +3652,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="180" spans="1:3">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A180" s="36">
         <v>4</v>
       </c>
@@ -3528,7 +3663,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="181" spans="1:3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A181" s="36">
         <v>4</v>
       </c>
@@ -3539,7 +3674,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="182" spans="1:3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A182" s="36">
         <v>4</v>
       </c>
@@ -3550,7 +3685,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="183" spans="1:3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A183" s="36">
         <v>4</v>
       </c>
@@ -3561,7 +3696,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="184" spans="1:3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A184" s="36">
         <v>4</v>
       </c>
@@ -3572,7 +3707,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A185" s="36">
         <v>4</v>
       </c>
@@ -3583,7 +3718,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="186" spans="1:3">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A186" s="36">
         <v>4</v>
       </c>
@@ -3594,7 +3729,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="187" spans="1:3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A187" s="36">
         <v>4</v>
       </c>
@@ -3605,7 +3740,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="188" spans="1:3">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A188" s="36">
         <v>4</v>
       </c>
@@ -3616,7 +3751,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="189" spans="1:3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A189" s="36">
         <v>4</v>
       </c>
@@ -3627,7 +3762,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="15.5">
+    <row r="190" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A190" s="36">
         <v>4</v>
       </c>
@@ -3638,7 +3773,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="191" spans="1:3">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A191" s="36">
         <v>4</v>
       </c>
@@ -3649,7 +3784,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="192" spans="1:3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A192" s="36">
         <v>4</v>
       </c>
@@ -3660,7 +3795,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="193" spans="1:3">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A193" s="36">
         <v>4</v>
       </c>
@@ -3671,7 +3806,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="194" spans="1:3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A194" s="36">
         <v>4</v>
       </c>
@@ -3682,7 +3817,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="195" spans="1:3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A195" s="36">
         <v>4</v>
       </c>
@@ -3693,7 +3828,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="196" spans="1:3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A196" s="36">
         <v>4</v>
       </c>
@@ -3704,7 +3839,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="197" spans="1:3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A197" s="36">
         <v>4</v>
       </c>
@@ -3715,7 +3850,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="198" spans="1:3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A198" s="36">
         <v>4</v>
       </c>
@@ -3726,7 +3861,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="199" spans="1:3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A199" s="36">
         <v>4</v>
       </c>
@@ -3737,7 +3872,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="200" spans="1:3">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A200" s="36">
         <v>4</v>
       </c>
@@ -3748,7 +3883,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="201" spans="1:3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A201" s="36">
         <v>4</v>
       </c>
@@ -3759,7 +3894,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="202" spans="1:3">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A202" s="36">
         <v>4</v>
       </c>
@@ -3770,7 +3905,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="203" spans="1:3">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A203" s="36">
         <v>4</v>
       </c>
@@ -3781,7 +3916,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="204" spans="1:3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A204" s="36">
         <v>4</v>
       </c>
@@ -3792,7 +3927,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="205" spans="1:3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A205" s="36">
         <v>4</v>
       </c>
@@ -3803,7 +3938,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="206" spans="1:3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A206" s="36">
         <v>4</v>
       </c>
@@ -3814,7 +3949,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="207" spans="1:3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A207" s="36">
         <v>4</v>
       </c>
@@ -3825,7 +3960,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15.5">
+    <row r="208" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A208" s="36">
         <v>4</v>
       </c>
@@ -3836,7 +3971,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="15" thickBot="1">
+    <row r="209" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="60">
         <v>4</v>
       </c>
@@ -3845,6 +3980,248 @@
       </c>
       <c r="C209" s="62" t="s">
         <v>213</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A210">
+        <v>3</v>
+      </c>
+      <c r="B210">
+        <v>410</v>
+      </c>
+      <c r="C210" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A211">
+        <v>3</v>
+      </c>
+      <c r="B211">
+        <v>411</v>
+      </c>
+      <c r="C211" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A212">
+        <v>3</v>
+      </c>
+      <c r="B212">
+        <v>414</v>
+      </c>
+      <c r="C212" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A213">
+        <v>3</v>
+      </c>
+      <c r="B213" s="61" t="s">
+        <v>272</v>
+      </c>
+      <c r="C213" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A214">
+        <v>3</v>
+      </c>
+      <c r="B214" s="61" t="s">
+        <v>273</v>
+      </c>
+      <c r="C214" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A215">
+        <v>3</v>
+      </c>
+      <c r="B215" s="61" t="s">
+        <v>274</v>
+      </c>
+      <c r="C215" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A216">
+        <v>3</v>
+      </c>
+      <c r="B216" s="61" t="s">
+        <v>275</v>
+      </c>
+      <c r="C216" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A217">
+        <v>3</v>
+      </c>
+      <c r="B217" t="s">
+        <v>256</v>
+      </c>
+      <c r="C217" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A218">
+        <v>3</v>
+      </c>
+      <c r="B218" s="61" t="s">
+        <v>276</v>
+      </c>
+      <c r="C218" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A219">
+        <v>4</v>
+      </c>
+      <c r="B219">
+        <v>422</v>
+      </c>
+      <c r="C219" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A220">
+        <v>4</v>
+      </c>
+      <c r="B220">
+        <v>424</v>
+      </c>
+      <c r="C220" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A221">
+        <v>4</v>
+      </c>
+      <c r="B221">
+        <v>426</v>
+      </c>
+      <c r="C221" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A222">
+        <v>4</v>
+      </c>
+      <c r="B222">
+        <v>427</v>
+      </c>
+      <c r="C222" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A223">
+        <v>4</v>
+      </c>
+      <c r="B223">
+        <v>432</v>
+      </c>
+      <c r="C223" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A224">
+        <v>4</v>
+      </c>
+      <c r="B224">
+        <v>433</v>
+      </c>
+      <c r="C224" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A225">
+        <v>4</v>
+      </c>
+      <c r="B225">
+        <v>434</v>
+      </c>
+      <c r="C225" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A226">
+        <v>4</v>
+      </c>
+      <c r="B226" s="61" t="s">
+        <v>277</v>
+      </c>
+      <c r="C226" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A227">
+        <v>4</v>
+      </c>
+      <c r="B227" s="61" t="s">
+        <v>278</v>
+      </c>
+      <c r="C227" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A228">
+        <v>4</v>
+      </c>
+      <c r="B228" s="61" t="s">
+        <v>279</v>
+      </c>
+      <c r="C228" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A229">
+        <v>4</v>
+      </c>
+      <c r="B229" t="s">
+        <v>268</v>
+      </c>
+      <c r="C229" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A230">
+        <v>4</v>
+      </c>
+      <c r="B230" s="61" t="s">
+        <v>280</v>
+      </c>
+      <c r="C230" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A231">
+        <v>4</v>
+      </c>
+      <c r="B231" s="61" t="s">
+        <v>281</v>
+      </c>
+      <c r="C231" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3855,15 +4232,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D596DB-28BB-4C17-8EAC-DE3B3C7E35BB}">
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:D36"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -3877,7 +4254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="18.5">
+    <row r="2" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A2" s="3">
         <v>0</v>
       </c>
@@ -3889,7 +4266,7 @@
       </c>
       <c r="D2" s="5"/>
     </row>
-    <row r="3" spans="1:4" ht="18.5">
+    <row r="3" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A3" s="3">
         <v>0</v>
       </c>
@@ -3901,7 +4278,7 @@
       </c>
       <c r="D3" s="5"/>
     </row>
-    <row r="4" spans="1:4" ht="18.5">
+    <row r="4" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -3913,7 +4290,7 @@
       </c>
       <c r="D4" s="5"/>
     </row>
-    <row r="5" spans="1:4" ht="18.5">
+    <row r="5" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
         <v>0</v>
       </c>
@@ -3925,7 +4302,7 @@
       </c>
       <c r="D5" s="5"/>
     </row>
-    <row r="6" spans="1:4" ht="23" customHeight="1">
+    <row r="6" spans="1:4" ht="23" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
         <v>0</v>
       </c>
@@ -3937,7 +4314,7 @@
       </c>
       <c r="D6" s="5"/>
     </row>
-    <row r="7" spans="1:4" ht="18.5">
+    <row r="7" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -3949,7 +4326,7 @@
       </c>
       <c r="D7" s="5"/>
     </row>
-    <row r="8" spans="1:4" ht="18.5">
+    <row r="8" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -3961,7 +4338,7 @@
       </c>
       <c r="D8" s="5"/>
     </row>
-    <row r="9" spans="1:4" ht="18.5">
+    <row r="9" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A9" s="6">
         <v>1</v>
       </c>
@@ -3973,7 +4350,7 @@
       </c>
       <c r="D9" s="5"/>
     </row>
-    <row r="10" spans="1:4" ht="18.5">
+    <row r="10" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>1</v>
       </c>
@@ -3985,7 +4362,7 @@
       </c>
       <c r="D10" s="5"/>
     </row>
-    <row r="11" spans="1:4" ht="18.5">
+    <row r="11" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -3997,7 +4374,7 @@
       </c>
       <c r="D11" s="5"/>
     </row>
-    <row r="12" spans="1:4" ht="18.5">
+    <row r="12" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -4009,7 +4386,7 @@
       </c>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:4" ht="18.5">
+    <row r="13" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>4</v>
       </c>
@@ -4021,7 +4398,7 @@
       </c>
       <c r="D13" s="5"/>
     </row>
-    <row r="14" spans="1:4" ht="18.5">
+    <row r="14" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>2</v>
       </c>
@@ -4033,7 +4410,7 @@
       </c>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" ht="18.5">
+    <row r="15" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A15" s="10">
         <v>3</v>
       </c>
@@ -4045,7 +4422,7 @@
       </c>
       <c r="D15" s="5"/>
     </row>
-    <row r="16" spans="1:4" ht="18.5">
+    <row r="16" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A16" s="10">
         <v>3</v>
       </c>
@@ -4057,7 +4434,7 @@
       </c>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" ht="18.5">
+    <row r="17" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A17" s="10">
         <v>3</v>
       </c>
@@ -4069,7 +4446,7 @@
       </c>
       <c r="D17" s="5"/>
     </row>
-    <row r="18" spans="1:4" ht="18.5">
+    <row r="18" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
         <v>3</v>
       </c>
@@ -4081,7 +4458,7 @@
       </c>
       <c r="D18" s="13"/>
     </row>
-    <row r="19" spans="1:4" ht="18.5">
+    <row r="19" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>3</v>
       </c>
@@ -4093,7 +4470,7 @@
       </c>
       <c r="D19" s="5"/>
     </row>
-    <row r="20" spans="1:4" ht="18.5">
+    <row r="20" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>4</v>
       </c>
@@ -4105,7 +4482,7 @@
       </c>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:4" ht="18.5">
+    <row r="21" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>4</v>
       </c>
@@ -4117,7 +4494,7 @@
       </c>
       <c r="D21" s="5"/>
     </row>
-    <row r="22" spans="1:4" ht="18.5">
+    <row r="22" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>4</v>
       </c>
@@ -4129,7 +4506,7 @@
       </c>
       <c r="D22" s="5"/>
     </row>
-    <row r="23" spans="1:4" ht="18.5">
+    <row r="23" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <v>4</v>
       </c>
@@ -4141,7 +4518,7 @@
       </c>
       <c r="D23" s="5"/>
     </row>
-    <row r="24" spans="1:4" ht="18.5">
+    <row r="24" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>4</v>
       </c>
@@ -4153,7 +4530,7 @@
       </c>
       <c r="D24" s="5"/>
     </row>
-    <row r="25" spans="1:4" ht="18.5">
+    <row r="25" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>4</v>
       </c>
@@ -4165,7 +4542,7 @@
       </c>
       <c r="D25" s="5"/>
     </row>
-    <row r="26" spans="1:4" ht="19" thickBot="1">
+    <row r="26" spans="1:4" ht="19" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="14">
         <v>4</v>
       </c>
@@ -4176,6 +4553,116 @@
         <v>6</v>
       </c>
       <c r="D26" s="16"/>
+    </row>
+    <row r="27" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C27" s="63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>283</v>
+      </c>
+      <c r="C28" s="63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29" t="s">
+        <v>284</v>
+      </c>
+      <c r="C29" s="63" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>285</v>
+      </c>
+      <c r="C30" s="63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31" t="s">
+        <v>286</v>
+      </c>
+      <c r="C31" s="63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32" t="s">
+        <v>287</v>
+      </c>
+      <c r="C32" s="63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>288</v>
+      </c>
+      <c r="C33" s="63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>289</v>
+      </c>
+      <c r="C34" s="63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>290</v>
+      </c>
+      <c r="C35" s="63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>291</v>
+      </c>
+      <c r="C36" s="63" t="s">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
